--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -576,7 +576,7 @@
   <si>
     <t>このインスタンスが外部から参照されるために使われるIDである。処方箋全体としてのIDとしては使用しない。  
 処方箋内で同一の用法をまとめて表記されるRp番号はこのIdentifier elementの別スライスで表現する。それ以外に任意のIDを付与してもよい。  
-このIDは業務手順によって定められた処方オーダに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバからサーバに転送されたとしても固定のものとして存続する。</t>
+このIDは業務手順によって定められた処方オーダに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバーからサーバーに転送されたとしても固定のものとして存続する。</t>
   </si>
   <si>
     <t>これは業務IDであって、リソースに対するIDではない。</t>
@@ -1451,7 +1451,7 @@
     <t>フリーテキストの投与方法の説明　SIG:用法</t>
   </si>
   <si>
-    <t>フリーテキストの投与量用法は、投与される投与量や用法が複雑すぎてコーディングできない場合に使用できる。コード化された投与量や用法が存在する場合、フリーテキストの投与量や用法は、人間に表示するためにまだ存在している可能性がある。  
+    <t>フリーテキストの投与量用法は、投与される投与量や用法が複雑すぎてコード化できない場合に使用できる。コード化された投与量や用法が存在する場合、フリーテキストの投与量や用法は、人間に表示するためにまだ存在している可能性がある。  
 投与量や用法のこの指示は、実際に投与される薬の投与量や用法を反映する必要がある。</t>
   </si>
   <si>
@@ -1676,7 +1676,7 @@
     <t>投与⽅法に対応するJAMI 用法コード表基本用法１桁コードを識別するURI。</t>
   </si>
   <si>
-    <t>コードは臨時で列記したものや、コードのリストからSNOMED CTのように公式に定義されたものまである（HL7 v3 core principle を参照)。FHIR自体ではコーディング規約を定めてはいないし、意味を暗示するために利用されない(SHALL NOT)。一般的に UserSelected = trueの場合には一つのコードシステムが使われる。</t>
+    <t>コードは臨時で列記したものや、コードのリストからSNOMED CTのように公式に定義されたものまである（HL7 v3 core principle を参照)。FHIR自体ではコード化に関する規約を定めてはいないし、意味を暗示するために利用されない(SHALL NOT)。一般的に UserSelected = trueの場合には一つのコードシステムが使われる。</t>
   </si>
   <si>
     <t>他のコードシステムへの変換や代替のコードシステムを使ってエンコードしてもよい。</t>
